--- a/data/WCC_Contract_Data.xlsx
+++ b/data/WCC_Contract_Data.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Programs'!$A$1:$D$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Intakes'!$A$1:$K$138</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fees'!$A$1:$W$275</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fees'!$A$1:$W$127</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Outline Map'!$A$1:$B$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="85" customWidth="1" min="1" max="1"/>
@@ -600,7 +600,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- One row per program + intake date + residency tier (domestic / international)</t>
+          <t>- One row per program + effective_from date + residency tier (domestic / international)</t>
         </is>
       </c>
     </row>
@@ -647,145 +647,152 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- To update fees: add new rows with a later effective_from date (old rows still apply to earlier intakes)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>INTAKES TAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>- One row per intake (enrollment window) per program</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>- hours, weeks, delivery method are PER COHORT — not per program</t>
+          <t>- One row per intake (enrollment window) per program</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>- domestic_delivery / international_delivery can differ for the same intake</t>
+          <t>- hours, weeks, delivery method are PER COHORT — not per program</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>- intake_date / end_date format: YYYY-MM-DD</t>
+          <t>- domestic_delivery / international_delivery can differ for the same intake</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>- intake_date / end_date format: YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>- status: Open = available, Closed = hidden from advisors, Waitlist = full but accepting</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>CONDITIONAL FORMATTING LEGEND</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  RED cells = blank required field or Closed status</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  YELLOW cells = $0 amount (verify if intentional) or Waitlist status</t>
+          <t xml:space="preserve">  RED cells = blank required field or Closed status</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GREEN cells = Open status</t>
+          <t xml:space="preserve">  YELLOW cells = $0 amount (verify if intentional) or Waitlist status</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t xml:space="preserve">  GREEN cells = Open status</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t xml:space="preserve">  BLUE cells = Scholarship (negative amount)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-    </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>COMMON MISTAKES TO AVOID</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>- Typo in program_name → fees not found, advisor sees $0 total</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>- Missing intake row → no fees for that cohort</t>
+          <t>- Typo in program_name → fees not found, advisor sees $0 total</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>- Positive number in Scholarship → validation will reject it</t>
+          <t>- Missing intake row → no fees for that cohort</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>- Wrong date format → use YYYY-MM-DD not MM/DD/YYYY</t>
+          <t>- Positive number in Scholarship → validation will reject it</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>- Adding $ sign or comma in fee amounts → validation will reject it</t>
+          <t>- Wrong date format → use YYYY-MM-DD not MM/DD/YYYY</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>- Adding $ sign or comma in fee amounts → validation will reject it</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>- Forgetting both domestic AND international rows for an intake</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-    </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Last updated: 2026-03-27 — v3 schema (column-based fees, scholarship support)</t>
         </is>
@@ -8555,7 +8562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W275"/>
+  <dimension ref="A1:W127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8591,7 +8598,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>intake_date</t>
+          <t>effective_from</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
@@ -8703,12 +8710,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Academic Preparation</t>
+          <t>Dementia Care</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8716,11 +8723,11 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n">
-        <v>280</v>
+      <c r="D2" s="5" t="n">
+        <v>50</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>700</v>
+        <v>175</v>
       </c>
       <c r="W2" s="6">
         <f>SUM(D2:V2)</f>
@@ -8730,12 +8737,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Academic Preparation</t>
+          <t>Dementia Care</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -8743,11 +8750,11 @@
           <t>international</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n">
-        <v>280</v>
+      <c r="D3" s="5" t="n">
+        <v>50</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>700</v>
+        <v>175</v>
       </c>
       <c r="W3" s="6">
         <f>SUM(D3:V3)</f>
@@ -8757,12 +8764,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Academic Preparation</t>
+          <t>Medication Management</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8770,11 +8777,14 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>280</v>
+      <c r="D4" s="5" t="n">
+        <v>50</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>700</v>
+        <v>175</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>175</v>
       </c>
       <c r="W4" s="6">
         <f>SUM(D4:V4)</f>
@@ -8784,12 +8794,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Academic Preparation</t>
+          <t>Medication Management</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8797,11 +8807,14 @@
           <t>international</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>280</v>
+      <c r="D5" s="5" t="n">
+        <v>50</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>700</v>
+        <v>175</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>175</v>
       </c>
       <c r="W5" s="6">
         <f>SUM(D5:V5)</f>
@@ -8811,12 +8824,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Accounting Diploma</t>
+          <t>Palliative Care</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8825,22 +8838,13 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>8490</v>
+        <v>175</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>610</v>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>200</v>
       </c>
       <c r="W6" s="6">
         <f>SUM(D6:V6)</f>
@@ -8850,12 +8854,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Accounting Diploma</t>
+          <t>Palliative Care</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8864,22 +8868,13 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>11700</v>
+        <v>175</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>610</v>
-      </c>
-      <c r="U7" s="5" t="n">
-        <v>200</v>
       </c>
       <c r="W7" s="6">
         <f>SUM(D7:V7)</f>
@@ -8889,12 +8884,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Accounting Diploma</t>
+          <t>Certificate in Makeup Artistry Fundamentals</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8905,20 +8900,14 @@
       <c r="D8" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="H8" s="5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>8490</v>
-      </c>
       <c r="L8" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>610</v>
-      </c>
-      <c r="U8" s="5" t="n">
-        <v>200</v>
+        <v>890</v>
       </c>
       <c r="W8" s="6">
         <f>SUM(D8:V8)</f>
@@ -8928,12 +8917,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Accounting Diploma</t>
+          <t>Certificate in Makeup Artistry Fundamentals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8944,20 +8933,14 @@
       <c r="D9" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="H9" s="5" t="n">
+        <v>3250</v>
+      </c>
+      <c r="J9" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>11700</v>
-      </c>
       <c r="L9" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>610</v>
-      </c>
-      <c r="U9" s="5" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="W9" s="6">
         <f>SUM(D9:V9)</f>
@@ -8967,12 +8950,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Accounting and Payroll Compliance Professional Certificate</t>
+          <t>Canadian Payroll Administration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8980,14 +8963,11 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>250</v>
+      <c r="E10" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6500</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>175</v>
@@ -9000,12 +8980,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Accounting and Payroll Compliance Professional Certificate</t>
+          <t>Canadian Payroll Administration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9013,14 +8993,11 @@
           <t>international</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>250</v>
+      <c r="E11" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>9500</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>175</v>
@@ -9033,12 +9010,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Accounting and Payroll Compliance Professional Certificate</t>
+          <t>Canadian Taxation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9046,14 +9023,11 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>250</v>
+      <c r="F12" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>6500</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>175</v>
@@ -9066,12 +9040,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Accounting and Payroll Compliance Professional Certificate</t>
+          <t>Canadian Taxation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9079,14 +9053,11 @@
           <t>international</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>250</v>
+      <c r="F13" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>9500</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L13" s="5" t="n">
         <v>175</v>
@@ -9099,12 +9070,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Activity Assistant Certificate</t>
+          <t>Quickbooks for Accounting</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9112,14 +9083,11 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>250</v>
+      <c r="E14" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>1900</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>175</v>
@@ -9132,12 +9100,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Activity Assistant Certificate</t>
+          <t>Quickbooks for Accounting</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9145,14 +9113,11 @@
           <t>international</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>250</v>
+      <c r="E15" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>2900</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>175</v>
@@ -9165,12 +9130,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Activity Assistant Certificate</t>
+          <t>Keyboarding Skills</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -9179,13 +9144,10 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>1900</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>175</v>
@@ -9198,12 +9160,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Activity Assistant Certificate</t>
+          <t>Keyboarding Skills</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -9212,13 +9174,10 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>2900</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>175</v>
@@ -9231,12 +9190,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Acute Care for HCAs</t>
+          <t>Food Service Assistant Certificate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9248,13 +9207,13 @@
         <v>250</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>2250</v>
+        <v>4420</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="W18" s="6">
         <f>SUM(D18:V18)</f>
@@ -9264,12 +9223,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Acute Care for HCAs</t>
+          <t>Food Service Assistant Certificate</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9281,13 +9240,13 @@
         <v>250</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>3250</v>
+        <v>5380</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="W19" s="6">
         <f>SUM(D19:V19)</f>
@@ -9297,12 +9256,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Acute Care for HCAs</t>
+          <t>Basics of Computers</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9310,14 +9269,11 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>250</v>
+      <c r="E20" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>200</v>
+        <v>375</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>175</v>
@@ -9330,12 +9286,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Acute Care for HCAs</t>
+          <t>Basics of Computers</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9343,14 +9299,11 @@
           <t>international</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>250</v>
+      <c r="E21" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>3250</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>200</v>
+        <v>375</v>
       </c>
       <c r="L21" s="5" t="n">
         <v>175</v>
@@ -9363,12 +9316,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Addictions Support Worker Diploma</t>
+          <t>Network Engineer Diploma</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -9380,13 +9333,13 @@
         <v>250</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>8000</v>
+        <v>17250</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1000</v>
+        <v>175</v>
       </c>
       <c r="W22" s="6">
         <f>SUM(D22:V22)</f>
@@ -9396,12 +9349,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Addictions Support Worker Diploma</t>
+          <t>Network Engineer Diploma</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -9413,13 +9366,13 @@
         <v>250</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>11500</v>
+        <v>20250</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>1000</v>
+        <v>175</v>
       </c>
       <c r="W23" s="6">
         <f>SUM(D23:V23)</f>
@@ -9429,12 +9382,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Addictions Support Worker Diploma</t>
+          <t>Information Systems Diploma</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9446,13 +9399,13 @@
         <v>250</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>8000</v>
+        <v>8320</v>
       </c>
       <c r="J24" s="5" t="n">
         <v>200</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>1000</v>
+        <v>780</v>
       </c>
       <c r="W24" s="6">
         <f>SUM(D24:V24)</f>
@@ -9462,12 +9415,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Addictions Support Worker Diploma</t>
+          <t>Information Systems Diploma</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9479,13 +9432,13 @@
         <v>250</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>11500</v>
+        <v>11960</v>
       </c>
       <c r="J25" s="5" t="n">
         <v>200</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>1000</v>
+        <v>780</v>
       </c>
       <c r="W25" s="6">
         <f>SUM(D25:V25)</f>
@@ -9495,12 +9448,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Advanced Accounting Diploma</t>
+          <t>Academic Preparation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -9508,20 +9461,11 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>250</v>
+      <c r="G26" s="5" t="n">
+        <v>280</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>16800</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="W26" s="6">
         <f>SUM(D26:V26)</f>
@@ -9531,12 +9475,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Advanced Accounting Diploma</t>
+          <t>Academic Preparation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9544,20 +9488,11 @@
           <t>international</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n">
-        <v>500</v>
+      <c r="G27" s="5" t="n">
+        <v>280</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>24150</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="W27" s="6">
         <f>SUM(D27:V27)</f>
@@ -9567,12 +9502,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Advanced Accounting Diploma</t>
+          <t>CLB Preparation</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -9581,19 +9516,13 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>16800</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>1500</v>
       </c>
       <c r="W28" s="6">
         <f>SUM(D28:V28)</f>
@@ -9603,12 +9532,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Advanced Accounting Diploma</t>
+          <t>CLB Preparation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9617,19 +9546,13 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>24150</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L29" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v>1500</v>
       </c>
       <c r="W29" s="6">
         <f>SUM(D29:V29)</f>
@@ -9639,12 +9562,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Airline Cabin Crew Diploma</t>
+          <t>IELTS Preparation</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9653,13 +9576,10 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>9500</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>400</v>
+        <v>675</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>175</v>
@@ -9672,12 +9592,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Airline Cabin Crew Diploma</t>
+          <t>IELTS Preparation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9686,13 +9606,10 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>12500</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>400</v>
+        <v>975</v>
       </c>
       <c r="L31" s="5" t="n">
         <v>175</v>
@@ -9705,12 +9622,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Airline Cabin Crew Diploma</t>
+          <t>Private Pilot License</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9721,14 +9638,29 @@
       <c r="D32" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H32" s="5" t="n">
-        <v>9500</v>
+      <c r="E32" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
       <c r="L32" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>8700</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>3375</v>
+      </c>
+      <c r="S32" s="5" t="n">
+        <v>1050</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>2250</v>
       </c>
       <c r="W32" s="6">
         <f>SUM(D32:V32)</f>
@@ -9738,12 +9670,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Airline Cabin Crew Diploma</t>
+          <t>Private Pilot License</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9754,14 +9686,29 @@
       <c r="D33" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H33" s="5" t="n">
-        <v>12500</v>
+      <c r="E33" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
       <c r="L33" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>8700</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>3375</v>
+      </c>
+      <c r="S33" s="5" t="n">
+        <v>1050</v>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>2250</v>
       </c>
       <c r="W33" s="6">
         <f>SUM(D33:V33)</f>
@@ -9771,12 +9718,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bachelor of Hospitality Management</t>
+          <t>Warehouse and Logistics Fundamentals Certificate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9787,14 +9734,11 @@
       <c r="D34" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="I34" s="5" t="n">
-        <v>520</v>
+      <c r="H34" s="5" t="n">
+        <v>4000</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>125</v>
+        <v>500</v>
       </c>
       <c r="W34" s="6">
         <f>SUM(D34:V34)</f>
@@ -9804,12 +9748,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bachelor of Hospitality Management</t>
+          <t>Warehouse and Logistics Fundamentals Certificate</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9820,14 +9764,11 @@
       <c r="D35" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="I35" s="5" t="n">
-        <v>330</v>
+      <c r="H35" s="5" t="n">
+        <v>6000</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v>125</v>
+        <v>500</v>
       </c>
       <c r="W35" s="6">
         <f>SUM(D35:V35)</f>
@@ -9837,12 +9778,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bachelor of Hospitality Management</t>
+          <t>Acute Care for HCAs</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -9853,14 +9794,14 @@
       <c r="D36" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="I36" s="5" t="n">
-        <v>520</v>
+      <c r="H36" s="5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>125</v>
       </c>
       <c r="W36" s="6">
         <f>SUM(D36:V36)</f>
@@ -9870,12 +9811,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bachelor of Hospitality Management</t>
+          <t>Acute Care for HCAs</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -9886,14 +9827,14 @@
       <c r="D37" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="I37" s="5" t="n">
-        <v>330</v>
+      <c r="H37" s="5" t="n">
+        <v>3250</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="L37" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v>125</v>
       </c>
       <c r="W37" s="6">
         <f>SUM(D37:V37)</f>
@@ -9903,12 +9844,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Basics of Computers</t>
+          <t>Advanced Accounting Diploma</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -9916,14 +9857,20 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n">
-        <v>100</v>
+      <c r="D38" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>375</v>
+        <v>16800</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>1500</v>
       </c>
       <c r="W38" s="6">
         <f>SUM(D38:V38)</f>
@@ -9933,12 +9880,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Basics of Computers</t>
+          <t>Advanced Accounting Diploma</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9946,14 +9893,20 @@
           <t>international</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n">
-        <v>100</v>
+      <c r="D39" s="5" t="n">
+        <v>500</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>375</v>
+        <v>24150</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>1500</v>
       </c>
       <c r="W39" s="6">
         <f>SUM(D39:V39)</f>
@@ -9963,12 +9916,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Basics of Computers</t>
+          <t>Business Essentials Certificate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9976,11 +9929,14 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n">
-        <v>100</v>
+      <c r="D40" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>375</v>
+        <v>2800</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>175</v>
@@ -9993,12 +9949,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Basics of Computers</t>
+          <t>Business Essentials Certificate</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -10006,11 +9962,14 @@
           <t>international</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n">
-        <v>100</v>
+      <c r="D41" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>375</v>
+        <v>4110</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="L41" s="5" t="n">
         <v>175</v>
@@ -10023,12 +9982,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bookkeeping and Accounting Certificate</t>
+          <t>Activity Assistant Certificate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -10040,16 +9999,13 @@
         <v>250</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>4165</v>
+        <v>1900</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="L42" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v>195</v>
       </c>
       <c r="W42" s="6">
         <f>SUM(D42:V42)</f>
@@ -10059,12 +10015,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bookkeeping and Accounting Certificate</t>
+          <t>Activity Assistant Certificate</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -10076,16 +10032,13 @@
         <v>250</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>6165</v>
+        <v>2900</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v>195</v>
       </c>
       <c r="W43" s="6">
         <f>SUM(D43:V43)</f>
@@ -10095,12 +10048,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bookkeeping and Accounting Certificate</t>
+          <t>Addictions Support Worker Diploma</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -10112,16 +10065,13 @@
         <v>250</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>4165</v>
+        <v>8000</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>195</v>
+        <v>1000</v>
       </c>
       <c r="W44" s="6">
         <f>SUM(D44:V44)</f>
@@ -10131,12 +10081,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bookkeeping and Accounting Certificate</t>
+          <t>Addictions Support Worker Diploma</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -10148,16 +10098,13 @@
         <v>250</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>6165</v>
+        <v>11500</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v>195</v>
+        <v>1000</v>
       </c>
       <c r="W45" s="6">
         <f>SUM(D45:V45)</f>
@@ -10167,12 +10114,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Business Essentials Certificate</t>
+          <t>Cloud Computing Specialist Diploma</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10184,10 +10131,10 @@
         <v>250</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>2800</v>
+        <v>24250</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>175</v>
@@ -10200,12 +10147,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Business Essentials Certificate</t>
+          <t>Cloud Computing Specialist Diploma</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -10217,10 +10164,10 @@
         <v>250</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>4110</v>
+        <v>29000</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="L47" s="5" t="n">
         <v>175</v>
@@ -10233,12 +10180,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Business Essentials Certificate</t>
+          <t>Post Graduate Diploma in Information Technology</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10250,13 +10197,10 @@
         <v>250</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>2800</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>200</v>
+        <v>18900</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>175</v>
+        <v>780</v>
       </c>
       <c r="W48" s="6">
         <f>SUM(D48:V48)</f>
@@ -10266,12 +10210,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Business Essentials Certificate</t>
+          <t>Post Graduate Diploma in Information Technology</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -10280,16 +10224,13 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>4110</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>200</v>
+        <v>23100</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>175</v>
+        <v>780</v>
       </c>
       <c r="W49" s="6">
         <f>SUM(D49:V49)</f>
@@ -10299,12 +10240,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Business Essentials Certificate</t>
+          <t>Post Graduate Diploma in Health Administration</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -10316,10 +10257,10 @@
         <v>250</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>2800</v>
+        <v>15000</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L50" s="5" t="n">
         <v>175</v>
@@ -10332,12 +10273,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Business Essentials Certificate</t>
+          <t>Post Graduate Diploma in Health Administration</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -10349,10 +10290,10 @@
         <v>250</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>4110</v>
+        <v>21000</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L51" s="5" t="n">
         <v>175</v>
@@ -10365,12 +10306,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Business Management Diploma</t>
+          <t>Post Graduate Diploma in Business Management</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -10381,20 +10322,17 @@
       <c r="D52" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E52" s="5" t="n">
-        <v>250</v>
-      </c>
       <c r="H52" s="5" t="n">
-        <v>8320</v>
+        <v>13440</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>175</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>834</v>
-      </c>
-      <c r="U52" s="5" t="n">
-        <v>100</v>
+        <v>960</v>
       </c>
       <c r="W52" s="6">
         <f>SUM(D52:V52)</f>
@@ -10404,12 +10342,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Business Management Diploma</t>
+          <t>Post Graduate Diploma in Business Management</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -10418,22 +10356,19 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>11700</v>
+        <v>19320</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="L53" s="5" t="n">
         <v>175</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>834</v>
-      </c>
-      <c r="U53" s="5" t="n">
-        <v>100</v>
+        <v>960</v>
       </c>
       <c r="W53" s="6">
         <f>SUM(D53:V53)</f>
@@ -10443,12 +10378,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Business Management Diploma</t>
+          <t>Network Administrator Diploma</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -10459,20 +10394,14 @@
       <c r="D54" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="H54" s="5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J54" s="5" t="n">
         <v>250</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>8320</v>
       </c>
       <c r="L54" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>834</v>
-      </c>
-      <c r="U54" s="5" t="n">
-        <v>100</v>
       </c>
       <c r="W54" s="6">
         <f>SUM(D54:V54)</f>
@@ -10482,12 +10411,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Business Management Diploma</t>
+          <t>Network Administrator Diploma</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -10498,20 +10427,14 @@
       <c r="D55" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E55" s="5" t="n">
+      <c r="H55" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J55" s="5" t="n">
         <v>250</v>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>11700</v>
       </c>
       <c r="L55" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="M55" s="5" t="n">
-        <v>834</v>
-      </c>
-      <c r="U55" s="5" t="n">
-        <v>100</v>
       </c>
       <c r="W55" s="6">
         <f>SUM(D55:V55)</f>
@@ -10521,12 +10444,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Business Management Diploma with Co-op</t>
+          <t>Community Mental Health Certificate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -10534,20 +10457,17 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="D56" s="5" t="n">
+      <c r="F56" s="5" t="n">
         <v>250</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>16800</v>
+        <v>1550</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="W56" s="6">
         <f>SUM(D56:V56)</f>
@@ -10557,12 +10477,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Management Diploma with Co-op</t>
+          <t>Community Mental Health Certificate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -10570,20 +10490,17 @@
           <t>international</t>
         </is>
       </c>
-      <c r="D57" s="5" t="n">
-        <v>500</v>
+      <c r="F57" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>24150</v>
+        <v>1550</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="W57" s="6">
         <f>SUM(D57:V57)</f>
@@ -10593,12 +10510,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Management Diploma with Co-op</t>
+          <t>Commercial Pilot License</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -10609,17 +10526,26 @@
       <c r="D58" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H58" s="5" t="n">
-        <v>16800</v>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>200</v>
-      </c>
       <c r="L58" s="5" t="n">
         <v>175</v>
       </c>
-      <c r="M58" s="5" t="n">
-        <v>900</v>
+      <c r="O58" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>10150</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>6750</v>
+      </c>
+      <c r="R58" s="5" t="n">
+        <v>20250</v>
+      </c>
+      <c r="S58" s="5" t="n">
+        <v>1050</v>
+      </c>
+      <c r="T58" s="5" t="n">
+        <v>7750</v>
       </c>
       <c r="W58" s="6">
         <f>SUM(D58:V58)</f>
@@ -10629,12 +10555,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Management Diploma with Co-op</t>
+          <t>Commercial Pilot License</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -10643,19 +10569,28 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>24150</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L59" s="5" t="n">
         <v>175</v>
       </c>
-      <c r="M59" s="5" t="n">
-        <v>900</v>
+      <c r="O59" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P59" s="5" t="n">
+        <v>10150</v>
+      </c>
+      <c r="Q59" s="5" t="n">
+        <v>6750</v>
+      </c>
+      <c r="R59" s="5" t="n">
+        <v>20250</v>
+      </c>
+      <c r="S59" s="5" t="n">
+        <v>1050</v>
+      </c>
+      <c r="T59" s="5" t="n">
+        <v>7750</v>
       </c>
       <c r="W59" s="6">
         <f>SUM(D59:V59)</f>
@@ -10665,12 +10600,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Management Diploma with Co-op</t>
+          <t>Airline Cabin Crew Diploma</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -10682,16 +10617,13 @@
         <v>250</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>16800</v>
+        <v>9500</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>900</v>
       </c>
       <c r="W60" s="6">
         <f>SUM(D60:V60)</f>
@@ -10701,12 +10633,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Business Management Diploma with Co-op</t>
+          <t>Airline Cabin Crew Diploma</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -10715,19 +10647,16 @@
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>24150</v>
+        <v>12500</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L61" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v>900</v>
       </c>
       <c r="W61" s="6">
         <f>SUM(D61:V61)</f>
@@ -10737,12 +10666,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CLB Preparation</t>
+          <t>Gerontology Diploma</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -10751,13 +10680,13 @@
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>400</v>
+        <v>6500</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>175</v>
+        <v>750</v>
       </c>
       <c r="W62" s="6">
         <f>SUM(D62:V62)</f>
@@ -10767,12 +10696,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CLB Preparation</t>
+          <t>Gerontology Diploma</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -10781,13 +10710,13 @@
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>400</v>
+        <v>8500</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>175</v>
+        <v>750</v>
       </c>
       <c r="W63" s="6">
         <f>SUM(D63:V63)</f>
@@ -10797,12 +10726,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CLB Preparation</t>
+          <t>Flight Instructor Rating Program</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -10811,10 +10740,10 @@
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>400</v>
+        <v>12550</v>
       </c>
       <c r="L64" s="5" t="n">
         <v>175</v>
@@ -10827,12 +10756,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CLB Preparation</t>
+          <t>Flight Instructor Rating Program</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10841,10 +10770,10 @@
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>400</v>
+        <v>12550</v>
       </c>
       <c r="L65" s="5" t="n">
         <v>175</v>
@@ -10857,12 +10786,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CLB Preparation</t>
+          <t>Pharmacy Assistant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10871,10 +10800,13 @@
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>400</v>
+        <v>6080</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>700</v>
       </c>
       <c r="L66" s="5" t="n">
         <v>175</v>
@@ -10887,12 +10819,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CLB Preparation</t>
+          <t>Pharmacy Assistant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10901,10 +10833,13 @@
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>400</v>
+        <v>8740</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>700</v>
       </c>
       <c r="L67" s="5" t="n">
         <v>175</v>
@@ -10917,12 +10852,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Canadian Payroll Administration</t>
+          <t>Computer Science Fundamentals Diploma</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -10930,14 +10865,14 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="E68" s="5" t="n">
-        <v>100</v>
+      <c r="D68" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>450</v>
+        <v>5250</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>175</v>
+        <v>500</v>
       </c>
       <c r="W68" s="6">
         <f>SUM(D68:V68)</f>
@@ -10947,12 +10882,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Canadian Payroll Administration</t>
+          <t>Computer Science Fundamentals Diploma</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -10960,14 +10895,14 @@
           <t>international</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>100</v>
+      <c r="D69" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>450</v>
+        <v>8250</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>175</v>
+        <v>500</v>
       </c>
       <c r="W69" s="6">
         <f>SUM(D69:V69)</f>
@@ -10977,12 +10912,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Canadian Payroll Administration</t>
+          <t>Network Support Technician</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10990,11 +10925,17 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="D70" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>5120</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="K70" s="5" t="n">
         <v>100</v>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v>450</v>
       </c>
       <c r="L70" s="5" t="n">
         <v>175</v>
@@ -11007,12 +10948,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Canadian Payroll Administration</t>
+          <t>Network Support Technician</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11020,11 +10961,17 @@
           <t>international</t>
         </is>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="D71" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>7360</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="K71" s="5" t="n">
         <v>100</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>450</v>
       </c>
       <c r="L71" s="5" t="n">
         <v>175</v>
@@ -11037,12 +10984,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Canadian Payroll Administration</t>
+          <t>Health Care Assistant Diploma (Access)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11050,11 +10997,14 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n">
-        <v>100</v>
+      <c r="D72" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>450</v>
+        <v>3150</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>75</v>
       </c>
       <c r="L72" s="5" t="n">
         <v>175</v>
@@ -11067,12 +11017,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Canadian Payroll Administration</t>
+          <t>Health Care Assistant Diploma (Access)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -11080,11 +11030,14 @@
           <t>international</t>
         </is>
       </c>
-      <c r="E73" s="5" t="n">
-        <v>100</v>
+      <c r="D73" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>450</v>
+        <v>5150</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>75</v>
       </c>
       <c r="L73" s="5" t="n">
         <v>175</v>
@@ -11097,12 +11050,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Canadian Taxation</t>
+          <t>Medical Office Assistant Diploma</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -11110,11 +11063,14 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>100</v>
+      <c r="D74" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>600</v>
+        <v>6290</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>400</v>
       </c>
       <c r="L74" s="5" t="n">
         <v>175</v>
@@ -11127,12 +11083,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Canadian Taxation</t>
+          <t>Medical Office Assistant Diploma</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -11140,11 +11096,14 @@
           <t>international</t>
         </is>
       </c>
-      <c r="F75" s="5" t="n">
-        <v>100</v>
+      <c r="D75" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>600</v>
+        <v>8290</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>400</v>
       </c>
       <c r="L75" s="5" t="n">
         <v>175</v>
@@ -11157,12 +11116,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Canadian Taxation</t>
+          <t>Business Management Diploma with Co-op</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -11170,14 +11129,20 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="F76" s="5" t="n">
-        <v>100</v>
+      <c r="D76" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>600</v>
+        <v>16800</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="L76" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>900</v>
       </c>
       <c r="W76" s="6">
         <f>SUM(D76:V76)</f>
@@ -11187,12 +11152,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Canadian Taxation</t>
+          <t>Business Management Diploma with Co-op</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -11200,14 +11165,20 @@
           <t>international</t>
         </is>
       </c>
-      <c r="F77" s="5" t="n">
-        <v>100</v>
+      <c r="D77" s="5" t="n">
+        <v>500</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>600</v>
+        <v>24150</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="L77" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>900</v>
       </c>
       <c r="W77" s="6">
         <f>SUM(D77:V77)</f>
@@ -11217,12 +11188,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Certificate in International Business</t>
+          <t>Dental Receptionist Certificate</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -11233,11 +11204,14 @@
       <c r="D78" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E78" s="5" t="n">
-        <v>250</v>
-      </c>
       <c r="H78" s="5" t="n">
-        <v>7500</v>
+        <v>3060</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>360</v>
       </c>
       <c r="L78" s="5" t="n">
         <v>175</v>
@@ -11250,12 +11224,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Certificate in International Business</t>
+          <t>Dental Receptionist Certificate</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -11266,11 +11240,14 @@
       <c r="D79" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E79" s="5" t="n">
-        <v>250</v>
-      </c>
       <c r="H79" s="5" t="n">
-        <v>10500</v>
+        <v>5060</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>360</v>
       </c>
       <c r="L79" s="5" t="n">
         <v>175</v>
@@ -11283,12 +11260,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Certificate in International Business</t>
+          <t>Education Assistant Diploma</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11299,14 +11276,14 @@
       <c r="D80" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E80" s="5" t="n">
+      <c r="H80" s="5" t="n">
+        <v>8260</v>
+      </c>
+      <c r="J80" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H80" s="5" t="n">
-        <v>7500</v>
-      </c>
       <c r="L80" s="5" t="n">
-        <v>175</v>
+        <v>890</v>
       </c>
       <c r="W80" s="6">
         <f>SUM(D80:V80)</f>
@@ -11316,12 +11293,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Certificate in International Business</t>
+          <t>Education Assistant Diploma</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11332,14 +11309,14 @@
       <c r="D81" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="H81" s="5" t="n">
+        <v>11480</v>
+      </c>
+      <c r="J81" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H81" s="5" t="n">
-        <v>10500</v>
-      </c>
       <c r="L81" s="5" t="n">
-        <v>175</v>
+        <v>890</v>
       </c>
       <c r="W81" s="6">
         <f>SUM(D81:V81)</f>
@@ -11349,12 +11326,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Certificate in International Trade</t>
+          <t>Office Administration Certificate</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11365,14 +11342,14 @@
       <c r="D82" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="H82" s="5" t="n">
+        <v>3250</v>
+      </c>
+      <c r="J82" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H82" s="5" t="n">
-        <v>3500</v>
-      </c>
       <c r="L82" s="5" t="n">
-        <v>175</v>
+        <v>890</v>
       </c>
       <c r="W82" s="6">
         <f>SUM(D82:V82)</f>
@@ -11382,12 +11359,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Certificate in International Trade</t>
+          <t>Office Administration Certificate</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11398,14 +11375,14 @@
       <c r="D83" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E83" s="5" t="n">
+      <c r="H83" s="5" t="n">
+        <v>5250</v>
+      </c>
+      <c r="J83" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H83" s="5" t="n">
-        <v>3500</v>
-      </c>
       <c r="L83" s="5" t="n">
-        <v>175</v>
+        <v>800</v>
       </c>
       <c r="W83" s="6">
         <f>SUM(D83:V83)</f>
@@ -11420,7 +11397,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11453,7 +11430,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11481,12 +11458,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Certificate in Makeup Artistry Fundamentals</t>
+          <t>Hospitality Management Diploma</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11498,13 +11475,16 @@
         <v>250</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>250</v>
+        <v>13000</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>861</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>890</v>
+        <v>175</v>
+      </c>
+      <c r="U86" s="5" t="n">
+        <v>240</v>
       </c>
       <c r="W86" s="6">
         <f>SUM(D86:V86)</f>
@@ -11514,12 +11494,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Certificate in Makeup Artistry Fundamentals</t>
+          <t>Hospitality Management Diploma</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -11530,14 +11510,20 @@
       <c r="D87" s="5" t="n">
         <v>250</v>
       </c>
+      <c r="E87" s="5" t="n">
+        <v>250</v>
+      </c>
       <c r="H87" s="5" t="n">
-        <v>3250</v>
-      </c>
-      <c r="J87" s="5" t="n">
-        <v>250</v>
+        <v>21600</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>861</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>800</v>
+        <v>175</v>
+      </c>
+      <c r="U87" s="5" t="n">
+        <v>240</v>
       </c>
       <c r="W87" s="6">
         <f>SUM(D87:V87)</f>
@@ -11547,12 +11533,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Certificate in Makeup Artistry Fundamentals</t>
+          <t>Accounting Diploma</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -11563,14 +11549,20 @@
       <c r="D88" s="5" t="n">
         <v>250</v>
       </c>
+      <c r="E88" s="5" t="n">
+        <v>250</v>
+      </c>
       <c r="H88" s="5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="J88" s="5" t="n">
-        <v>250</v>
+        <v>8490</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>890</v>
+        <v>175</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>610</v>
+      </c>
+      <c r="U88" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="W88" s="6">
         <f>SUM(D88:V88)</f>
@@ -11580,12 +11572,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Certificate in Makeup Artistry Fundamentals</t>
+          <t>Accounting Diploma</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -11596,14 +11588,20 @@
       <c r="D89" s="5" t="n">
         <v>250</v>
       </c>
+      <c r="E89" s="5" t="n">
+        <v>250</v>
+      </c>
       <c r="H89" s="5" t="n">
-        <v>3250</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>250</v>
+        <v>11700</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>800</v>
+        <v>175</v>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>610</v>
+      </c>
+      <c r="U89" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="W89" s="6">
         <f>SUM(D89:V89)</f>
@@ -11613,12 +11611,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Computing Specialist Diploma</t>
+          <t>Certificate in International Business</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -11629,11 +11627,11 @@
       <c r="D90" s="5" t="n">
         <v>250</v>
       </c>
+      <c r="E90" s="5" t="n">
+        <v>250</v>
+      </c>
       <c r="H90" s="5" t="n">
-        <v>24250</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>500</v>
+        <v>7500</v>
       </c>
       <c r="L90" s="5" t="n">
         <v>175</v>
@@ -11646,12 +11644,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cloud Computing Specialist Diploma</t>
+          <t>Certificate in International Business</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -11662,11 +11660,11 @@
       <c r="D91" s="5" t="n">
         <v>250</v>
       </c>
+      <c r="E91" s="5" t="n">
+        <v>250</v>
+      </c>
       <c r="H91" s="5" t="n">
-        <v>29000</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>500</v>
+        <v>10500</v>
       </c>
       <c r="L91" s="5" t="n">
         <v>175</v>
@@ -11679,12 +11677,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Computing Specialist Diploma</t>
+          <t>Early Childhood Education Assistant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -11696,13 +11694,10 @@
         <v>250</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>24250</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>175</v>
+        <v>1830</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>120</v>
       </c>
       <c r="W92" s="6">
         <f>SUM(D92:V92)</f>
@@ -11712,12 +11707,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Computing Specialist Diploma</t>
+          <t>Early Childhood Education Assistant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -11729,13 +11724,10 @@
         <v>250</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>29000</v>
-      </c>
-      <c r="J93" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>175</v>
+        <v>2230</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>120</v>
       </c>
       <c r="W93" s="6">
         <f>SUM(D93:V93)</f>
@@ -11745,12 +11737,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Commercial Pilot License</t>
+          <t>English as a Second Language</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -11758,29 +11750,14 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="D94" s="5" t="n">
+      <c r="F94" s="5" t="n">
         <v>250</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>4150</v>
       </c>
       <c r="L94" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="O94" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P94" s="5" t="n">
-        <v>10150</v>
-      </c>
-      <c r="Q94" s="5" t="n">
-        <v>6750</v>
-      </c>
-      <c r="R94" s="5" t="n">
-        <v>20250</v>
-      </c>
-      <c r="S94" s="5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="T94" s="5" t="n">
-        <v>7750</v>
       </c>
       <c r="W94" s="6">
         <f>SUM(D94:V94)</f>
@@ -11790,12 +11767,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Commercial Pilot License</t>
+          <t>English as a Second Language</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -11803,29 +11780,14 @@
           <t>international</t>
         </is>
       </c>
-      <c r="D95" s="5" t="n">
+      <c r="F95" s="5" t="n">
         <v>250</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>5100</v>
       </c>
       <c r="L95" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="O95" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P95" s="5" t="n">
-        <v>10150</v>
-      </c>
-      <c r="Q95" s="5" t="n">
-        <v>6750</v>
-      </c>
-      <c r="R95" s="5" t="n">
-        <v>20250</v>
-      </c>
-      <c r="S95" s="5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="T95" s="5" t="n">
-        <v>7750</v>
       </c>
       <c r="W95" s="6">
         <f>SUM(D95:V95)</f>
@@ -11835,12 +11797,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Commercial Pilot License</t>
+          <t>Medical Device Reprocessing Technician Certificate</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -11851,26 +11813,17 @@
       <c r="D96" s="5" t="n">
         <v>250</v>
       </c>
+      <c r="H96" s="5" t="n">
+        <v>8500</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>430</v>
+      </c>
       <c r="L96" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="O96" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P96" s="5" t="n">
-        <v>10150</v>
-      </c>
-      <c r="Q96" s="5" t="n">
-        <v>6750</v>
-      </c>
-      <c r="R96" s="5" t="n">
-        <v>20250</v>
-      </c>
-      <c r="S96" s="5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="T96" s="5" t="n">
-        <v>7750</v>
       </c>
       <c r="W96" s="6">
         <f>SUM(D96:V96)</f>
@@ -11880,12 +11833,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Commercial Pilot License</t>
+          <t>Medical Device Reprocessing Technician Certificate</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -11896,26 +11849,17 @@
       <c r="D97" s="5" t="n">
         <v>250</v>
       </c>
+      <c r="H97" s="5" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>430</v>
+      </c>
       <c r="L97" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="O97" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P97" s="5" t="n">
-        <v>10150</v>
-      </c>
-      <c r="Q97" s="5" t="n">
-        <v>6750</v>
-      </c>
-      <c r="R97" s="5" t="n">
-        <v>20250</v>
-      </c>
-      <c r="S97" s="5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="T97" s="5" t="n">
-        <v>7750</v>
       </c>
       <c r="W97" s="6">
         <f>SUM(D97:V97)</f>
@@ -11925,12 +11869,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Community Mental Health Certificate</t>
+          <t>Medical Laboratory Assistant</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -11938,17 +11882,23 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="F98" s="5" t="n">
+      <c r="D98" s="5" t="n">
         <v>250</v>
       </c>
+      <c r="E98" s="5" t="n">
+        <v>250</v>
+      </c>
       <c r="H98" s="5" t="n">
-        <v>1550</v>
+        <v>13100</v>
       </c>
       <c r="J98" s="5" t="n">
         <v>300</v>
       </c>
+      <c r="K98" s="5" t="n">
+        <v>500</v>
+      </c>
       <c r="L98" s="5" t="n">
-        <v>890</v>
+        <v>175</v>
       </c>
       <c r="W98" s="6">
         <f>SUM(D98:V98)</f>
@@ -11958,12 +11908,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Community Mental Health Certificate</t>
+          <t>Medical Laboratory Assistant</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -11971,17 +11921,23 @@
           <t>international</t>
         </is>
       </c>
-      <c r="F99" s="5" t="n">
+      <c r="D99" s="5" t="n">
         <v>250</v>
       </c>
+      <c r="E99" s="5" t="n">
+        <v>250</v>
+      </c>
       <c r="H99" s="5" t="n">
-        <v>1550</v>
+        <v>18100</v>
       </c>
       <c r="J99" s="5" t="n">
         <v>300</v>
       </c>
+      <c r="K99" s="5" t="n">
+        <v>500</v>
+      </c>
       <c r="L99" s="5" t="n">
-        <v>800</v>
+        <v>175</v>
       </c>
       <c r="W99" s="6">
         <f>SUM(D99:V99)</f>
@@ -11991,12 +11947,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Community Mental Health Certificate</t>
+          <t>Night Rating Program</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -12004,17 +11960,20 @@
           <t>domestic</t>
         </is>
       </c>
-      <c r="F100" s="5" t="n">
+      <c r="D100" s="5" t="n">
         <v>250</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>1550</v>
+        <v>3900</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>890</v>
+        <v>175</v>
+      </c>
+      <c r="U100" s="5" t="n">
+        <v>600</v>
       </c>
       <c r="W100" s="6">
         <f>SUM(D100:V100)</f>
@@ -12024,12 +11983,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Community Mental Health Certificate</t>
+          <t>Night Rating Program</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -12037,17 +11996,20 @@
           <t>international</t>
         </is>
       </c>
-      <c r="F101" s="5" t="n">
+      <c r="D101" s="5" t="n">
         <v>250</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>1550</v>
+        <v>3900</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>800</v>
+        <v>175</v>
+      </c>
+      <c r="U101" s="5" t="n">
+        <v>600</v>
       </c>
       <c r="W101" s="6">
         <f>SUM(D101:V101)</f>
@@ -12057,12 +12019,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Community Support Worker Diploma</t>
+          <t>Live in Caregiver Certificate</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -12074,13 +12036,16 @@
         <v>250</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>8670</v>
+        <v>4000</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>195</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>750</v>
+        <v>890</v>
       </c>
       <c r="W102" s="6">
         <f>SUM(D102:V102)</f>
@@ -12090,12 +12055,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Community Support Worker Diploma</t>
+          <t>Live in Caregiver Certificate</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -12107,13 +12072,16 @@
         <v>250</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>13060</v>
+        <v>7000</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>195</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="W103" s="6">
         <f>SUM(D103:V103)</f>
@@ -12123,12 +12091,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Community Support Worker Diploma</t>
+          <t>Paralegal Diploma</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -12140,13 +12108,13 @@
         <v>250</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>8670</v>
+        <v>16450</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>750</v>
+        <v>150</v>
       </c>
       <c r="W104" s="6">
         <f>SUM(D104:V104)</f>
@@ -12156,12 +12124,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Community Support Worker Diploma</t>
+          <t>Paralegal Diploma</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -12170,16 +12138,16 @@
         </is>
       </c>
       <c r="D105" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>23775</v>
+      </c>
+      <c r="J105" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H105" s="5" t="n">
-        <v>13060</v>
-      </c>
-      <c r="J105" s="5" t="n">
-        <v>100</v>
-      </c>
       <c r="L105" s="5" t="n">
-        <v>750</v>
+        <v>150</v>
       </c>
       <c r="W105" s="6">
         <f>SUM(D105:V105)</f>
@@ -12189,12 +12157,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Computer Science Fundamentals Diploma</t>
+          <t>Dental Assistant Diploma</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -12206,9 +12174,15 @@
         <v>250</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>5250</v>
+        <v>14000</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>500</v>
       </c>
       <c r="L106" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="U106" s="5" t="n">
         <v>500</v>
       </c>
       <c r="W106" s="6">
@@ -12219,12 +12193,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Computer Science Fundamentals Diploma</t>
+          <t>Dental Assistant Diploma</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -12236,9 +12210,15 @@
         <v>250</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>8250</v>
+        <v>19200</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>500</v>
       </c>
       <c r="L107" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="U107" s="5" t="n">
         <v>500</v>
       </c>
       <c r="W107" s="6">
@@ -12249,12 +12229,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Computer Science Fundamentals Diploma</t>
+          <t>Bachelor of Hospitality Management</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -12265,11 +12245,14 @@
       <c r="D108" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H108" s="5" t="n">
-        <v>5250</v>
+      <c r="I108" s="5" t="n">
+        <v>520</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>500</v>
+        <v>175</v>
+      </c>
+      <c r="N108" s="5" t="n">
+        <v>125</v>
       </c>
       <c r="W108" s="6">
         <f>SUM(D108:V108)</f>
@@ -12279,12 +12262,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Computer Science Fundamentals Diploma</t>
+          <t>Bachelor of Hospitality Management</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -12295,11 +12278,14 @@
       <c r="D109" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="H109" s="5" t="n">
-        <v>8250</v>
+      <c r="I109" s="5" t="n">
+        <v>330</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>500</v>
+        <v>175</v>
+      </c>
+      <c r="N109" s="5" t="n">
+        <v>125</v>
       </c>
       <c r="W109" s="6">
         <f>SUM(D109:V109)</f>
@@ -12309,12 +12295,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Dementia Care</t>
+          <t>Business Management Diploma</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -12323,10 +12309,22 @@
         </is>
       </c>
       <c r="D110" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H110" s="5" t="n">
+        <v>8320</v>
+      </c>
+      <c r="L110" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="M110" s="5" t="n">
+        <v>834</v>
+      </c>
+      <c r="U110" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="W110" s="6">
         <f>SUM(D110:V110)</f>
@@ -12336,12 +12334,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Dementia Care</t>
+          <t>Business Management Diploma</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -12350,10 +12348,22 @@
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="H111" s="5" t="n">
+        <v>11700</v>
+      </c>
+      <c r="L111" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="M111" s="5" t="n">
+        <v>834</v>
+      </c>
+      <c r="U111" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="W111" s="6">
         <f>SUM(D111:V111)</f>
@@ -12363,12 +12373,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Dementia Care</t>
+          <t>Accounting and Payroll Compliance Professional Certificate</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -12377,9 +12387,15 @@
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="H112" s="5" t="n">
+        <v>6500</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L112" s="5" t="n">
         <v>175</v>
       </c>
       <c r="W112" s="6">
@@ -12390,12 +12406,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Dementia Care</t>
+          <t>Accounting and Payroll Compliance Professional Certificate</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -12404,9 +12420,15 @@
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="H113" s="5" t="n">
+        <v>9500</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L113" s="5" t="n">
         <v>175</v>
       </c>
       <c r="W113" s="6">
@@ -12417,12 +12439,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Dementia Care</t>
+          <t>Bookkeeping and Accounting Certificate</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -12431,10 +12453,19 @@
         </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="H114" s="5" t="n">
+        <v>4165</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="L114" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="M114" s="5" t="n">
+        <v>195</v>
       </c>
       <c r="W114" s="6">
         <f>SUM(D114:V114)</f>
@@ -12444,12 +12475,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Dementia Care</t>
+          <t>Bookkeeping and Accounting Certificate</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -12458,10 +12489,19 @@
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="H115" s="5" t="n">
+        <v>6165</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="L115" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="M115" s="5" t="n">
+        <v>195</v>
       </c>
       <c r="W115" s="6">
         <f>SUM(D115:V115)</f>
@@ -12471,12 +12511,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Dental Assistant Diploma</t>
+          <t>Health Care Assistant Diploma</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -12488,16 +12528,13 @@
         <v>250</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>14000</v>
+        <v>7000</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L116" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="U116" s="5" t="n">
-        <v>500</v>
       </c>
       <c r="W116" s="6">
         <f>SUM(D116:V116)</f>
@@ -12507,12 +12544,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Dental Assistant Diploma</t>
+          <t>Health Care Assistant Diploma</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -12524,16 +12561,13 @@
         <v>250</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>19200</v>
+        <v>9000</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L117" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="U117" s="5" t="n">
-        <v>500</v>
       </c>
       <c r="W117" s="6">
         <f>SUM(D117:V117)</f>
@@ -12543,12 +12577,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Dental Assistant Diploma</t>
+          <t>Health Care Assistant with ESL Diploma</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -12560,16 +12594,13 @@
         <v>250</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>14000</v>
+        <v>7250</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L118" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="U118" s="5" t="n">
-        <v>500</v>
       </c>
       <c r="W118" s="6">
         <f>SUM(D118:V118)</f>
@@ -12579,12 +12610,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dental Assistant Diploma</t>
+          <t>Health Care Assistant with ESL Diploma</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -12596,16 +12627,13 @@
         <v>250</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>19200</v>
+        <v>12750</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L119" s="5" t="n">
         <v>175</v>
-      </c>
-      <c r="U119" s="5" t="n">
-        <v>500</v>
       </c>
       <c r="W119" s="6">
         <f>SUM(D119:V119)</f>
@@ -12615,12 +12643,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Dental Receptionist Certificate</t>
+          <t>Pharmacy Technician Diploma Program</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -12632,13 +12660,13 @@
         <v>250</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>3060</v>
+        <v>14950</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>360</v>
+        <v>700</v>
       </c>
       <c r="L120" s="5" t="n">
         <v>175</v>
@@ -12651,12 +12679,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Dental Receptionist Certificate</t>
+          <t>Pharmacy Technician Diploma Program</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -12668,13 +12696,13 @@
         <v>250</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>5060</v>
+        <v>17950</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>360</v>
+        <v>700</v>
       </c>
       <c r="L121" s="5" t="n">
         <v>175</v>
@@ -12687,12 +12715,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Dental Receptionist Certificate</t>
+          <t>Registered Massage Therapy Program</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -12704,16 +12732,16 @@
         <v>250</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>3060</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>200</v>
+        <v>36042</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>360</v>
+        <v>1235</v>
       </c>
       <c r="L122" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="U122" s="5" t="n">
+        <v>700</v>
       </c>
       <c r="W122" s="6">
         <f>SUM(D122:V122)</f>
@@ -12723,12 +12751,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Dental Receptionist Certificate</t>
+          <t>Registered Massage Therapy Program</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -12740,16 +12768,16 @@
         <v>250</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>5060</v>
-      </c>
-      <c r="J123" s="5" t="n">
-        <v>200</v>
+        <v>46042</v>
       </c>
       <c r="K123" s="5" t="n">
-        <v>360</v>
+        <v>1235</v>
       </c>
       <c r="L123" s="5" t="n">
         <v>175</v>
+      </c>
+      <c r="U123" s="5" t="n">
+        <v>700</v>
       </c>
       <c r="W123" s="6">
         <f>SUM(D123:V123)</f>
@@ -12759,12 +12787,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Early Childhood Education</t>
+          <t>Community Support Worker Diploma</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -12775,20 +12803,14 @@
       <c r="D124" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E124" s="5" t="n">
-        <v>250</v>
-      </c>
       <c r="H124" s="5" t="n">
-        <v>17810</v>
+        <v>8670</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="K124" s="5" t="n">
-        <v>530</v>
+        <v>100</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>175</v>
+        <v>750</v>
       </c>
       <c r="W124" s="6">
         <f>SUM(D124:V124)</f>
@@ -12798,12 +12820,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Early Childhood Education</t>
+          <t>Community Support Worker Diploma</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -12814,20 +12836,14 @@
       <c r="D125" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E125" s="5" t="n">
-        <v>250</v>
-      </c>
       <c r="H125" s="5" t="n">
-        <v>22060</v>
+        <v>13060</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="K125" s="5" t="n">
-        <v>530</v>
+        <v>100</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>175</v>
+        <v>750</v>
       </c>
       <c r="W125" s="6">
         <f>SUM(D125:V125)</f>
@@ -12842,7 +12858,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -12881,7 +12897,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -12912,4949 +12928,8 @@
         <v/>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Early Childhood Education Assistant</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H128" s="5" t="n">
-        <v>1830</v>
-      </c>
-      <c r="K128" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="W128" s="6">
-        <f>SUM(D128:V128)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Early Childhood Education Assistant</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H129" s="5" t="n">
-        <v>2230</v>
-      </c>
-      <c r="K129" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="W129" s="6">
-        <f>SUM(D129:V129)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Early Childhood Education Assistant</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H130" s="5" t="n">
-        <v>1830</v>
-      </c>
-      <c r="K130" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="W130" s="6">
-        <f>SUM(D130:V130)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Early Childhood Education Assistant</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>2230</v>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="W131" s="6">
-        <f>SUM(D131:V131)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Education Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H132" s="5" t="n">
-        <v>8260</v>
-      </c>
-      <c r="J132" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L132" s="5" t="n">
-        <v>890</v>
-      </c>
-      <c r="W132" s="6">
-        <f>SUM(D132:V132)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Education Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H133" s="5" t="n">
-        <v>11480</v>
-      </c>
-      <c r="J133" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L133" s="5" t="n">
-        <v>890</v>
-      </c>
-      <c r="W133" s="6">
-        <f>SUM(D133:V133)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Education Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>8260</v>
-      </c>
-      <c r="J134" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L134" s="5" t="n">
-        <v>890</v>
-      </c>
-      <c r="W134" s="6">
-        <f>SUM(D134:V134)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Education Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H135" s="5" t="n">
-        <v>11480</v>
-      </c>
-      <c r="J135" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L135" s="5" t="n">
-        <v>890</v>
-      </c>
-      <c r="W135" s="6">
-        <f>SUM(D135:V135)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>English as a Second Language</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H136" s="5" t="n">
-        <v>4150</v>
-      </c>
-      <c r="L136" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W136" s="6">
-        <f>SUM(D136:V136)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>English as a Second Language</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H137" s="5" t="n">
-        <v>5100</v>
-      </c>
-      <c r="L137" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W137" s="6">
-        <f>SUM(D137:V137)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>English as a Second Language</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2027-01-06</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H138" s="5" t="n">
-        <v>4150</v>
-      </c>
-      <c r="L138" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W138" s="6">
-        <f>SUM(D138:V138)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>English as a Second Language</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>2027-01-06</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H139" s="5" t="n">
-        <v>5100</v>
-      </c>
-      <c r="L139" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W139" s="6">
-        <f>SUM(D139:V139)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Flight Instructor Rating Program</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H140" s="5" t="n">
-        <v>12550</v>
-      </c>
-      <c r="L140" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W140" s="6">
-        <f>SUM(D140:V140)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Flight Instructor Rating Program</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H141" s="5" t="n">
-        <v>12550</v>
-      </c>
-      <c r="L141" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W141" s="6">
-        <f>SUM(D141:V141)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Flight Instructor Rating Program</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H142" s="5" t="n">
-        <v>12550</v>
-      </c>
-      <c r="L142" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W142" s="6">
-        <f>SUM(D142:V142)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Flight Instructor Rating Program</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H143" s="5" t="n">
-        <v>12550</v>
-      </c>
-      <c r="L143" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W143" s="6">
-        <f>SUM(D143:V143)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Food Service Assistant Certificate</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D144" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H144" s="5" t="n">
-        <v>4420</v>
-      </c>
-      <c r="J144" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L144" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="W144" s="6">
-        <f>SUM(D144:V144)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Food Service Assistant Certificate</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H145" s="5" t="n">
-        <v>5380</v>
-      </c>
-      <c r="J145" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L145" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="W145" s="6">
-        <f>SUM(D145:V145)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Food Service Assistant Certificate</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D146" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H146" s="5" t="n">
-        <v>4420</v>
-      </c>
-      <c r="J146" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L146" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="W146" s="6">
-        <f>SUM(D146:V146)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Food Service Assistant Certificate</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H147" s="5" t="n">
-        <v>5380</v>
-      </c>
-      <c r="J147" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L147" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="W147" s="6">
-        <f>SUM(D147:V147)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Gerontology Diploma</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D148" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H148" s="5" t="n">
-        <v>6500</v>
-      </c>
-      <c r="L148" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="W148" s="6">
-        <f>SUM(D148:V148)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Gerontology Diploma</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H149" s="5" t="n">
-        <v>8500</v>
-      </c>
-      <c r="L149" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="W149" s="6">
-        <f>SUM(D149:V149)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Gerontology Diploma</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2027-02-17</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D150" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H150" s="5" t="n">
-        <v>6500</v>
-      </c>
-      <c r="L150" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="W150" s="6">
-        <f>SUM(D150:V150)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Gerontology Diploma</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2027-02-17</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D151" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H151" s="5" t="n">
-        <v>8500</v>
-      </c>
-      <c r="L151" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="W151" s="6">
-        <f>SUM(D151:V151)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Health Care Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D152" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H152" s="5" t="n">
-        <v>7000</v>
-      </c>
-      <c r="J152" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L152" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W152" s="6">
-        <f>SUM(D152:V152)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Health Care Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D153" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H153" s="5" t="n">
-        <v>9000</v>
-      </c>
-      <c r="J153" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L153" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W153" s="6">
-        <f>SUM(D153:V153)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Health Care Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D154" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H154" s="5" t="n">
-        <v>7000</v>
-      </c>
-      <c r="J154" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L154" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W154" s="6">
-        <f>SUM(D154:V154)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Health Care Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H155" s="5" t="n">
-        <v>9000</v>
-      </c>
-      <c r="J155" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L155" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W155" s="6">
-        <f>SUM(D155:V155)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Health Care Assistant Diploma (Access)</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H156" s="5" t="n">
-        <v>3150</v>
-      </c>
-      <c r="J156" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L156" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W156" s="6">
-        <f>SUM(D156:V156)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Health Care Assistant Diploma (Access)</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H157" s="5" t="n">
-        <v>5150</v>
-      </c>
-      <c r="J157" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L157" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W157" s="6">
-        <f>SUM(D157:V157)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Health Care Assistant Diploma (Access)</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D158" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H158" s="5" t="n">
-        <v>3150</v>
-      </c>
-      <c r="J158" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L158" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W158" s="6">
-        <f>SUM(D158:V158)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Health Care Assistant Diploma (Access)</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H159" s="5" t="n">
-        <v>5150</v>
-      </c>
-      <c r="J159" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L159" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W159" s="6">
-        <f>SUM(D159:V159)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Health Care Assistant with ESL Diploma</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2027-01-06</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D160" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H160" s="5" t="n">
-        <v>7250</v>
-      </c>
-      <c r="J160" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L160" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W160" s="6">
-        <f>SUM(D160:V160)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Health Care Assistant with ESL Diploma</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2027-01-06</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H161" s="5" t="n">
-        <v>12750</v>
-      </c>
-      <c r="J161" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L161" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W161" s="6">
-        <f>SUM(D161:V161)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Health Care Assistant with ESL Diploma</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2027-02-03</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D162" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H162" s="5" t="n">
-        <v>7250</v>
-      </c>
-      <c r="J162" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L162" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W162" s="6">
-        <f>SUM(D162:V162)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Health Care Assistant with ESL Diploma</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2027-02-03</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H163" s="5" t="n">
-        <v>12750</v>
-      </c>
-      <c r="J163" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="L163" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W163" s="6">
-        <f>SUM(D163:V163)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Hospitality Management Diploma</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D164" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H164" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="K164" s="5" t="n">
-        <v>861</v>
-      </c>
-      <c r="L164" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U164" s="5" t="n">
-        <v>240</v>
-      </c>
-      <c r="W164" s="6">
-        <f>SUM(D164:V164)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Hospitality Management Diploma</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D165" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E165" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H165" s="5" t="n">
-        <v>21600</v>
-      </c>
-      <c r="K165" s="5" t="n">
-        <v>861</v>
-      </c>
-      <c r="L165" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U165" s="5" t="n">
-        <v>240</v>
-      </c>
-      <c r="W165" s="6">
-        <f>SUM(D165:V165)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Hospitality Management Diploma</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D166" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H166" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="K166" s="5" t="n">
-        <v>861</v>
-      </c>
-      <c r="L166" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U166" s="5" t="n">
-        <v>240</v>
-      </c>
-      <c r="W166" s="6">
-        <f>SUM(D166:V166)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Hospitality Management Diploma</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D167" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E167" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H167" s="5" t="n">
-        <v>21600</v>
-      </c>
-      <c r="K167" s="5" t="n">
-        <v>861</v>
-      </c>
-      <c r="L167" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U167" s="5" t="n">
-        <v>240</v>
-      </c>
-      <c r="W167" s="6">
-        <f>SUM(D167:V167)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Hospitality Management Diploma</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D168" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H168" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="K168" s="5" t="n">
-        <v>861</v>
-      </c>
-      <c r="L168" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U168" s="5" t="n">
-        <v>240</v>
-      </c>
-      <c r="W168" s="6">
-        <f>SUM(D168:V168)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Hospitality Management Diploma</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D169" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E169" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H169" s="5" t="n">
-        <v>21600</v>
-      </c>
-      <c r="K169" s="5" t="n">
-        <v>861</v>
-      </c>
-      <c r="L169" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U169" s="5" t="n">
-        <v>240</v>
-      </c>
-      <c r="W169" s="6">
-        <f>SUM(D169:V169)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>IELTS Preparation</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D170" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H170" s="5" t="n">
-        <v>675</v>
-      </c>
-      <c r="L170" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W170" s="6">
-        <f>SUM(D170:V170)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>IELTS Preparation</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D171" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H171" s="5" t="n">
-        <v>975</v>
-      </c>
-      <c r="L171" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W171" s="6">
-        <f>SUM(D171:V171)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>IELTS Preparation</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D172" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H172" s="5" t="n">
-        <v>675</v>
-      </c>
-      <c r="L172" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W172" s="6">
-        <f>SUM(D172:V172)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>IELTS Preparation</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D173" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H173" s="5" t="n">
-        <v>975</v>
-      </c>
-      <c r="L173" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W173" s="6">
-        <f>SUM(D173:V173)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Information Systems Diploma</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D174" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H174" s="5" t="n">
-        <v>8320</v>
-      </c>
-      <c r="J174" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="L174" s="5" t="n">
-        <v>780</v>
-      </c>
-      <c r="W174" s="6">
-        <f>SUM(D174:V174)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Information Systems Diploma</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D175" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H175" s="5" t="n">
-        <v>11960</v>
-      </c>
-      <c r="J175" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="L175" s="5" t="n">
-        <v>780</v>
-      </c>
-      <c r="W175" s="6">
-        <f>SUM(D175:V175)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Information Systems Diploma</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D176" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H176" s="5" t="n">
-        <v>8320</v>
-      </c>
-      <c r="J176" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="L176" s="5" t="n">
-        <v>780</v>
-      </c>
-      <c r="W176" s="6">
-        <f>SUM(D176:V176)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Information Systems Diploma</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D177" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H177" s="5" t="n">
-        <v>11960</v>
-      </c>
-      <c r="J177" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="L177" s="5" t="n">
-        <v>780</v>
-      </c>
-      <c r="W177" s="6">
-        <f>SUM(D177:V177)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Keyboarding Skills</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D178" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H178" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L178" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W178" s="6">
-        <f>SUM(D178:V178)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Keyboarding Skills</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D179" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H179" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L179" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W179" s="6">
-        <f>SUM(D179:V179)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Keyboarding Skills</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D180" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H180" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L180" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W180" s="6">
-        <f>SUM(D180:V180)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Keyboarding Skills</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D181" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H181" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L181" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W181" s="6">
-        <f>SUM(D181:V181)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Keyboarding Skills</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D182" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H182" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L182" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W182" s="6">
-        <f>SUM(D182:V182)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Keyboarding Skills</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H183" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L183" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W183" s="6">
-        <f>SUM(D183:V183)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Live in Caregiver Certificate</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D184" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H184" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J184" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="K184" s="5" t="n">
-        <v>195</v>
-      </c>
-      <c r="L184" s="5" t="n">
-        <v>890</v>
-      </c>
-      <c r="W184" s="6">
-        <f>SUM(D184:V184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Live in Caregiver Certificate</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H185" s="5" t="n">
-        <v>7000</v>
-      </c>
-      <c r="J185" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="K185" s="5" t="n">
-        <v>195</v>
-      </c>
-      <c r="L185" s="5" t="n">
-        <v>800</v>
-      </c>
-      <c r="W185" s="6">
-        <f>SUM(D185:V185)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Live in Caregiver Certificate</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H186" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J186" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="K186" s="5" t="n">
-        <v>195</v>
-      </c>
-      <c r="L186" s="5" t="n">
-        <v>890</v>
-      </c>
-      <c r="W186" s="6">
-        <f>SUM(D186:V186)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Live in Caregiver Certificate</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>7000</v>
-      </c>
-      <c r="J187" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="K187" s="5" t="n">
-        <v>195</v>
-      </c>
-      <c r="L187" s="5" t="n">
-        <v>800</v>
-      </c>
-      <c r="W187" s="6">
-        <f>SUM(D187:V187)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Medical Device Reprocessing Technician Certificate</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D188" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H188" s="5" t="n">
-        <v>8500</v>
-      </c>
-      <c r="J188" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="K188" s="5" t="n">
-        <v>430</v>
-      </c>
-      <c r="L188" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W188" s="6">
-        <f>SUM(D188:V188)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Medical Device Reprocessing Technician Certificate</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D189" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H189" s="5" t="n">
-        <v>10500</v>
-      </c>
-      <c r="J189" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="K189" s="5" t="n">
-        <v>430</v>
-      </c>
-      <c r="L189" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W189" s="6">
-        <f>SUM(D189:V189)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Medical Device Reprocessing Technician Certificate</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D190" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H190" s="5" t="n">
-        <v>8500</v>
-      </c>
-      <c r="J190" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="K190" s="5" t="n">
-        <v>430</v>
-      </c>
-      <c r="L190" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W190" s="6">
-        <f>SUM(D190:V190)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Medical Device Reprocessing Technician Certificate</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D191" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H191" s="5" t="n">
-        <v>10500</v>
-      </c>
-      <c r="J191" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="K191" s="5" t="n">
-        <v>430</v>
-      </c>
-      <c r="L191" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W191" s="6">
-        <f>SUM(D191:V191)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Medical Laboratory Assistant</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D192" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E192" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H192" s="5" t="n">
-        <v>13100</v>
-      </c>
-      <c r="J192" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="K192" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L192" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W192" s="6">
-        <f>SUM(D192:V192)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Medical Laboratory Assistant</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D193" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E193" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H193" s="5" t="n">
-        <v>18100</v>
-      </c>
-      <c r="J193" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="K193" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L193" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W193" s="6">
-        <f>SUM(D193:V193)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Medical Laboratory Assistant</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D194" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E194" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H194" s="5" t="n">
-        <v>13100</v>
-      </c>
-      <c r="J194" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="K194" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L194" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W194" s="6">
-        <f>SUM(D194:V194)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Medical Laboratory Assistant</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D195" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E195" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H195" s="5" t="n">
-        <v>18100</v>
-      </c>
-      <c r="J195" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="K195" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L195" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W195" s="6">
-        <f>SUM(D195:V195)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Medical Office Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D196" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H196" s="5" t="n">
-        <v>6290</v>
-      </c>
-      <c r="K196" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="L196" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W196" s="6">
-        <f>SUM(D196:V196)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Medical Office Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D197" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H197" s="5" t="n">
-        <v>8290</v>
-      </c>
-      <c r="K197" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="L197" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W197" s="6">
-        <f>SUM(D197:V197)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Medical Office Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>2027-02-17</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D198" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H198" s="5" t="n">
-        <v>6290</v>
-      </c>
-      <c r="K198" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="L198" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W198" s="6">
-        <f>SUM(D198:V198)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Medical Office Assistant Diploma</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>2027-02-17</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D199" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H199" s="5" t="n">
-        <v>8290</v>
-      </c>
-      <c r="K199" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="L199" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W199" s="6">
-        <f>SUM(D199:V199)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Medication Management</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D200" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H200" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="L200" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W200" s="6">
-        <f>SUM(D200:V200)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Medication Management</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D201" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H201" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="L201" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W201" s="6">
-        <f>SUM(D201:V201)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Medication Management</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D202" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H202" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="L202" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W202" s="6">
-        <f>SUM(D202:V202)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Medication Management</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D203" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H203" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="L203" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W203" s="6">
-        <f>SUM(D203:V203)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Network Administrator Diploma</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D204" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H204" s="5" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J204" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L204" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W204" s="6">
-        <f>SUM(D204:V204)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Network Administrator Diploma</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D205" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H205" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J205" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L205" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W205" s="6">
-        <f>SUM(D205:V205)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Network Administrator Diploma</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D206" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H206" s="5" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J206" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L206" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W206" s="6">
-        <f>SUM(D206:V206)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Network Administrator Diploma</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D207" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H207" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J207" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L207" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W207" s="6">
-        <f>SUM(D207:V207)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Network Engineer Diploma</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D208" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H208" s="5" t="n">
-        <v>17250</v>
-      </c>
-      <c r="J208" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L208" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W208" s="6">
-        <f>SUM(D208:V208)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Network Engineer Diploma</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D209" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H209" s="5" t="n">
-        <v>20250</v>
-      </c>
-      <c r="J209" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L209" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W209" s="6">
-        <f>SUM(D209:V209)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Network Engineer Diploma</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D210" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H210" s="5" t="n">
-        <v>17250</v>
-      </c>
-      <c r="J210" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L210" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W210" s="6">
-        <f>SUM(D210:V210)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Network Engineer Diploma</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D211" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H211" s="5" t="n">
-        <v>20250</v>
-      </c>
-      <c r="J211" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L211" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W211" s="6">
-        <f>SUM(D211:V211)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Network Support Technician</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H212" s="5" t="n">
-        <v>5120</v>
-      </c>
-      <c r="J212" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="K212" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L212" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W212" s="6">
-        <f>SUM(D212:V212)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Network Support Technician</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D213" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H213" s="5" t="n">
-        <v>7360</v>
-      </c>
-      <c r="J213" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="K213" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L213" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W213" s="6">
-        <f>SUM(D213:V213)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Network Support Technician</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D214" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H214" s="5" t="n">
-        <v>5120</v>
-      </c>
-      <c r="J214" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="K214" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L214" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W214" s="6">
-        <f>SUM(D214:V214)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Network Support Technician</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D215" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H215" s="5" t="n">
-        <v>7360</v>
-      </c>
-      <c r="J215" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="K215" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L215" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W215" s="6">
-        <f>SUM(D215:V215)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Night Rating Program</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D216" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H216" s="5" t="n">
-        <v>3900</v>
-      </c>
-      <c r="J216" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="L216" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U216" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="W216" s="6">
-        <f>SUM(D216:V216)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Night Rating Program</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D217" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H217" s="5" t="n">
-        <v>3900</v>
-      </c>
-      <c r="J217" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="L217" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U217" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="W217" s="6">
-        <f>SUM(D217:V217)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Night Rating Program</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D218" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H218" s="5" t="n">
-        <v>3900</v>
-      </c>
-      <c r="J218" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="L218" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U218" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="W218" s="6">
-        <f>SUM(D218:V218)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Night Rating Program</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D219" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H219" s="5" t="n">
-        <v>3900</v>
-      </c>
-      <c r="J219" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="L219" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U219" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="W219" s="6">
-        <f>SUM(D219:V219)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Office Administration Certificate</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D220" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H220" s="5" t="n">
-        <v>3250</v>
-      </c>
-      <c r="J220" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L220" s="5" t="n">
-        <v>890</v>
-      </c>
-      <c r="W220" s="6">
-        <f>SUM(D220:V220)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Office Administration Certificate</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D221" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H221" s="5" t="n">
-        <v>5250</v>
-      </c>
-      <c r="J221" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L221" s="5" t="n">
-        <v>800</v>
-      </c>
-      <c r="W221" s="6">
-        <f>SUM(D221:V221)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Office Administration Certificate</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D222" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H222" s="5" t="n">
-        <v>3250</v>
-      </c>
-      <c r="J222" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L222" s="5" t="n">
-        <v>890</v>
-      </c>
-      <c r="W222" s="6">
-        <f>SUM(D222:V222)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Office Administration Certificate</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D223" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H223" s="5" t="n">
-        <v>5250</v>
-      </c>
-      <c r="J223" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L223" s="5" t="n">
-        <v>800</v>
-      </c>
-      <c r="W223" s="6">
-        <f>SUM(D223:V223)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Palliative Care</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D224" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H224" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="L224" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W224" s="6">
-        <f>SUM(D224:V224)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Palliative Care</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D225" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H225" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="L225" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W225" s="6">
-        <f>SUM(D225:V225)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Palliative Care</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D226" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H226" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="L226" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W226" s="6">
-        <f>SUM(D226:V226)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Palliative Care</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D227" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H227" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="L227" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W227" s="6">
-        <f>SUM(D227:V227)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Paralegal Diploma</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D228" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H228" s="5" t="n">
-        <v>16450</v>
-      </c>
-      <c r="J228" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L228" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="W228" s="6">
-        <f>SUM(D228:V228)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Paralegal Diploma</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D229" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="H229" s="5" t="n">
-        <v>23775</v>
-      </c>
-      <c r="J229" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L229" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="W229" s="6">
-        <f>SUM(D229:V229)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Paralegal Diploma</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D230" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H230" s="5" t="n">
-        <v>16450</v>
-      </c>
-      <c r="J230" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L230" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="W230" s="6">
-        <f>SUM(D230:V230)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Paralegal Diploma</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D231" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="H231" s="5" t="n">
-        <v>23775</v>
-      </c>
-      <c r="J231" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L231" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="W231" s="6">
-        <f>SUM(D231:V231)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Paralegal Diploma</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D232" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H232" s="5" t="n">
-        <v>16450</v>
-      </c>
-      <c r="J232" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L232" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="W232" s="6">
-        <f>SUM(D232:V232)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Paralegal Diploma</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D233" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="H233" s="5" t="n">
-        <v>23775</v>
-      </c>
-      <c r="J233" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L233" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="W233" s="6">
-        <f>SUM(D233:V233)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Pharmacy Assistant</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D234" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H234" s="5" t="n">
-        <v>6080</v>
-      </c>
-      <c r="K234" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="L234" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W234" s="6">
-        <f>SUM(D234:V234)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Pharmacy Assistant</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D235" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H235" s="5" t="n">
-        <v>8740</v>
-      </c>
-      <c r="K235" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="L235" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W235" s="6">
-        <f>SUM(D235:V235)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Pharmacy Assistant</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D236" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H236" s="5" t="n">
-        <v>6080</v>
-      </c>
-      <c r="K236" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="L236" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W236" s="6">
-        <f>SUM(D236:V236)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Pharmacy Assistant</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H237" s="5" t="n">
-        <v>8740</v>
-      </c>
-      <c r="K237" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="L237" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W237" s="6">
-        <f>SUM(D237:V237)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Pharmacy Technician Diploma Program</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H238" s="5" t="n">
-        <v>14950</v>
-      </c>
-      <c r="J238" s="5" t="n">
-        <v>950</v>
-      </c>
-      <c r="K238" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="L238" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W238" s="6">
-        <f>SUM(D238:V238)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>Pharmacy Technician Diploma Program</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H239" s="5" t="n">
-        <v>17950</v>
-      </c>
-      <c r="J239" s="5" t="n">
-        <v>950</v>
-      </c>
-      <c r="K239" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="L239" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W239" s="6">
-        <f>SUM(D239:V239)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>Pharmacy Technician Diploma Program</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H240" s="5" t="n">
-        <v>14950</v>
-      </c>
-      <c r="J240" s="5" t="n">
-        <v>950</v>
-      </c>
-      <c r="K240" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="L240" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W240" s="6">
-        <f>SUM(D240:V240)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>Pharmacy Technician Diploma Program</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H241" s="5" t="n">
-        <v>17950</v>
-      </c>
-      <c r="J241" s="5" t="n">
-        <v>950</v>
-      </c>
-      <c r="K241" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="L241" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W241" s="6">
-        <f>SUM(D241:V241)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Business Management</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H242" s="5" t="n">
-        <v>13440</v>
-      </c>
-      <c r="J242" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="L242" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M242" s="5" t="n">
-        <v>960</v>
-      </c>
-      <c r="W242" s="6">
-        <f>SUM(D242:V242)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Business Management</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D243" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="H243" s="5" t="n">
-        <v>19320</v>
-      </c>
-      <c r="J243" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="L243" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M243" s="5" t="n">
-        <v>960</v>
-      </c>
-      <c r="W243" s="6">
-        <f>SUM(D243:V243)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Business Management</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D244" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H244" s="5" t="n">
-        <v>13440</v>
-      </c>
-      <c r="J244" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="L244" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M244" s="5" t="n">
-        <v>960</v>
-      </c>
-      <c r="W244" s="6">
-        <f>SUM(D244:V244)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Business Management</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D245" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="H245" s="5" t="n">
-        <v>19320</v>
-      </c>
-      <c r="J245" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="L245" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="M245" s="5" t="n">
-        <v>960</v>
-      </c>
-      <c r="W245" s="6">
-        <f>SUM(D245:V245)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Health Administration</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D246" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H246" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J246" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L246" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W246" s="6">
-        <f>SUM(D246:V246)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Health Administration</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D247" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H247" s="5" t="n">
-        <v>21000</v>
-      </c>
-      <c r="J247" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L247" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W247" s="6">
-        <f>SUM(D247:V247)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Health Administration</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D248" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H248" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J248" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L248" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W248" s="6">
-        <f>SUM(D248:V248)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Health Administration</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D249" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H249" s="5" t="n">
-        <v>21000</v>
-      </c>
-      <c r="J249" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L249" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W249" s="6">
-        <f>SUM(D249:V249)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Health Administration</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D250" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H250" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J250" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L250" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W250" s="6">
-        <f>SUM(D250:V250)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Health Administration</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D251" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H251" s="5" t="n">
-        <v>21000</v>
-      </c>
-      <c r="J251" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L251" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W251" s="6">
-        <f>SUM(D251:V251)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Information Technology</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D252" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H252" s="5" t="n">
-        <v>18900</v>
-      </c>
-      <c r="L252" s="5" t="n">
-        <v>780</v>
-      </c>
-      <c r="W252" s="6">
-        <f>SUM(D252:V252)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Information Technology</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D253" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="H253" s="5" t="n">
-        <v>23100</v>
-      </c>
-      <c r="L253" s="5" t="n">
-        <v>780</v>
-      </c>
-      <c r="W253" s="6">
-        <f>SUM(D253:V253)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Information Technology</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>2027-02-03</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D254" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H254" s="5" t="n">
-        <v>18900</v>
-      </c>
-      <c r="L254" s="5" t="n">
-        <v>780</v>
-      </c>
-      <c r="W254" s="6">
-        <f>SUM(D254:V254)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>Post Graduate Diploma in Information Technology</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>2027-02-03</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D255" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="H255" s="5" t="n">
-        <v>23100</v>
-      </c>
-      <c r="L255" s="5" t="n">
-        <v>780</v>
-      </c>
-      <c r="W255" s="6">
-        <f>SUM(D255:V255)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>Private Pilot License</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D256" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E256" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="J256" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="L256" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="O256" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="P256" s="5" t="n">
-        <v>8700</v>
-      </c>
-      <c r="Q256" s="5" t="n">
-        <v>3375</v>
-      </c>
-      <c r="S256" s="5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="T256" s="5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="W256" s="6">
-        <f>SUM(D256:V256)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>Private Pilot License</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D257" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E257" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="J257" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="L257" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="O257" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="P257" s="5" t="n">
-        <v>8700</v>
-      </c>
-      <c r="Q257" s="5" t="n">
-        <v>3375</v>
-      </c>
-      <c r="S257" s="5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="T257" s="5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="W257" s="6">
-        <f>SUM(D257:V257)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>Private Pilot License</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D258" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E258" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="J258" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="L258" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="O258" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="P258" s="5" t="n">
-        <v>8700</v>
-      </c>
-      <c r="Q258" s="5" t="n">
-        <v>3375</v>
-      </c>
-      <c r="S258" s="5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="T258" s="5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="W258" s="6">
-        <f>SUM(D258:V258)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>Private Pilot License</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D259" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E259" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="J259" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="L259" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="O259" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="P259" s="5" t="n">
-        <v>8700</v>
-      </c>
-      <c r="Q259" s="5" t="n">
-        <v>3375</v>
-      </c>
-      <c r="S259" s="5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="T259" s="5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="W259" s="6">
-        <f>SUM(D259:V259)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>Quickbooks for Accounting</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="E260" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H260" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="L260" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W260" s="6">
-        <f>SUM(D260:V260)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Quickbooks for Accounting</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="E261" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H261" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="L261" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W261" s="6">
-        <f>SUM(D261:V261)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Quickbooks for Accounting</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="E262" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H262" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="L262" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W262" s="6">
-        <f>SUM(D262:V262)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Quickbooks for Accounting</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="E263" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H263" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="L263" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W263" s="6">
-        <f>SUM(D263:V263)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>Quickbooks for Accounting</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="E264" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H264" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="L264" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W264" s="6">
-        <f>SUM(D264:V264)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>Quickbooks for Accounting</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="E265" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H265" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="L265" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="W265" s="6">
-        <f>SUM(D265:V265)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>Registered Massage Therapy Program</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H266" s="5" t="n">
-        <v>36042</v>
-      </c>
-      <c r="K266" s="5" t="n">
-        <v>1235</v>
-      </c>
-      <c r="L266" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U266" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="W266" s="6">
-        <f>SUM(D266:V266)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>Registered Massage Therapy Program</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H267" s="5" t="n">
-        <v>46042</v>
-      </c>
-      <c r="K267" s="5" t="n">
-        <v>1235</v>
-      </c>
-      <c r="L267" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U267" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="W267" s="6">
-        <f>SUM(D267:V267)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>Registered Massage Therapy Program</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H268" s="5" t="n">
-        <v>36042</v>
-      </c>
-      <c r="K268" s="5" t="n">
-        <v>1235</v>
-      </c>
-      <c r="L268" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U268" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="W268" s="6">
-        <f>SUM(D268:V268)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>Registered Massage Therapy Program</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H269" s="5" t="n">
-        <v>46042</v>
-      </c>
-      <c r="K269" s="5" t="n">
-        <v>1235</v>
-      </c>
-      <c r="L269" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U269" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="W269" s="6">
-        <f>SUM(D269:V269)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>Registered Massage Therapy Program</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>2027-02-17</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H270" s="5" t="n">
-        <v>36042</v>
-      </c>
-      <c r="K270" s="5" t="n">
-        <v>1235</v>
-      </c>
-      <c r="L270" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U270" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="W270" s="6">
-        <f>SUM(D270:V270)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>Registered Massage Therapy Program</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>2027-02-17</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H271" s="5" t="n">
-        <v>46042</v>
-      </c>
-      <c r="K271" s="5" t="n">
-        <v>1235</v>
-      </c>
-      <c r="L271" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="U271" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="W271" s="6">
-        <f>SUM(D271:V271)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>Warehouse and Logistics Fundamentals Certificate</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D272" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H272" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="L272" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="W272" s="6">
-        <f>SUM(D272:V272)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>Warehouse and Logistics Fundamentals Certificate</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D273" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H273" s="5" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L273" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="W273" s="6">
-        <f>SUM(D273:V273)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Warehouse and Logistics Fundamentals Certificate</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>domestic</t>
-        </is>
-      </c>
-      <c r="D274" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H274" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="L274" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="W274" s="6">
-        <f>SUM(D274:V274)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Warehouse and Logistics Fundamentals Certificate</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="D275" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H275" s="5" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L275" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="W275" s="6">
-        <f>SUM(D275:V275)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W275"/>
+  <autoFilter ref="A1:W127"/>
   <conditionalFormatting sqref="A2:A500">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISBLANK(A2)</formula>

--- a/data/WCC_Contract_Data.xlsx
+++ b/data/WCC_Contract_Data.xlsx
@@ -680,7 +680,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>- domestic_delivery / international_delivery can differ for the same intake</t>
+          <t>- domestic_delivery_method / international_delivery_method can differ for the same intake</t>
         </is>
       </c>
     </row>
@@ -2261,8 +2261,8 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>domestic_delivery</t>
+          <t>domestic_delivery_method</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>international_delivery</t>
+          <t>international_delivery_method</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">

--- a/data/WCC_Contract_Data.xlsx
+++ b/data/WCC_Contract_Data.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Programs'!$A$1:$D$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Intakes'!$A$1:$K$138</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fees'!$A$1:$W$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Outline Map'!$A$1:$B$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Outline Map'!$A$1:$C$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13058,11 +13058,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13076,6 +13077,11 @@
           <t>outline_filename</t>
         </is>
       </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>google_drive_file_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13088,6 +13094,11 @@
           <t>Dementia_Care_Program_Outline</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1Bc7UIrxQyvTuAuSWhdr_KptjQIVOKUSk</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13100,6 +13111,11 @@
           <t>Medication_Management_Program_Outline</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1MEFLML2M1qf4tUzEOT2WQ3XcryBUCbrU</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13112,6 +13128,11 @@
           <t>Palliative_Care_Program_Outline</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>17TXHg3Ez31zF_r0RV5MRqTX-ZlexcJv3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13124,6 +13145,11 @@
           <t>Make_Up_Artistry_Fundamentals_Program_Outline</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1YhsdKwPcwkCoDpQsHVf5HWnz_uHe-ONm</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13132,6 +13158,7 @@
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13144,6 +13171,11 @@
           <t>Canadian_Taxation_Program_Outline</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>13JBtrsK9Rpd2jxcrRCtFwD30q3IGVXk7</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13152,6 +13184,7 @@
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13164,6 +13197,11 @@
           <t>Keyboarding_Skills_Program_Outline</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16mn2MMiTLi8nqRho2ShQXBYNhwKENX6w</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13176,6 +13214,11 @@
           <t>Food_Service_Assistant_Certificate_Program_Outline</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11nYt04usy7ap10IKrc2UhH-_m39l_6Oq</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13188,6 +13231,11 @@
           <t>Basics_of_Computers_Program_Outline</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>197Izf-lTwBjzSy-IVMy3P4smUQAXDhLN</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13200,6 +13248,11 @@
           <t>Network_Engineer_Program_Outline</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1Gfj6Ew2SVEA-Yi8CEaSXJGhbEQ59Zc7B</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13212,6 +13265,11 @@
           <t>Information_System_Program_Outline</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1syRGM5mpId4o2KEJiGz18UhAK81CgFjT</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13224,6 +13282,11 @@
           <t>Academic_Prep_Program_Outline</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1WqWJei6peDj7ABCYzzot5Fbi7uYExPir</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13236,6 +13299,11 @@
           <t>CLB_Test_Preparation_Program_Outline</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1y9ghwixoXnGBGlY4nPw5QLoW5_BID70V</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13248,6 +13316,11 @@
           <t>IELTS_Preparation_Program_Outline</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1gRQHCaEVHYZ6JqhVRj2pRBT2in2pwuf5</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13260,6 +13333,11 @@
           <t>Private_Pilot_License_Program_Outline</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10EZByQPgfWic2QU3vxTj7Bs3c-S8sAqp</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13272,6 +13350,11 @@
           <t>Warehouse_and_Logistics_Fundamentals_Program_Outline</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15-5UkT6JXUSwrlYqdsQvj7wZY3wvN41-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13284,6 +13367,11 @@
           <t>Acute_Care_for_HCAs_Program_Outline</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1_9BNJf_UgjUMNjkzLCtlYDpCo48roXHr</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13296,6 +13384,11 @@
           <t>Accounting_Management_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>17rUFwCuBvliA8oLAKHnUfjYn4SCJ7Up8</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13308,6 +13401,11 @@
           <t>Certificate_in_Business_Essentials_Program_Outline</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1r02JVQo0whIbYtQCsYl1QQy4qy8vQEFQ</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13320,6 +13418,11 @@
           <t>Activity_Assistant_Certificate_Program_Outline</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>13o9OozmUdgok3TGSO8N3kYlN5qcdotqO</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13332,6 +13435,11 @@
           <t>Addictions_Support_Worker_Program_Outline</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1h0kd0kUaEHWW8oGVtACnlW4Rxx7XroUE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13344,6 +13452,11 @@
           <t>Cloud_Computing_Technology_Program_Outline</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>15Enn_eFMUhU-qOTtToH2aiPHGxk_lpQm</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13356,6 +13469,11 @@
           <t>Digital_Technology_Solutions_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16EvFsTvd2hr6BezZelVKwLC-zdGHvPEz</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13368,6 +13486,11 @@
           <t>Health_Services_Administration_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1lxqJBlpc98WqkEwf4UkEYRxL58BtG6-d</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13380,6 +13503,11 @@
           <t>Integrated_Business_Management_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1471TFOycepRTKxRQmVsngyFBjZRR4acX</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13392,6 +13520,11 @@
           <t>Network_Administrator_Program_Outline</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1Y08vVYt2Y4KSHejvGFupGPjbTbyva2gS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13404,6 +13537,11 @@
           <t>Community_Mental_Health_Certificate_Program_Outline</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>12llLz-fdi_MSiDC5gNZrszXFydb3JjXI</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13416,6 +13554,11 @@
           <t>Commercial_Pilot_License_Program_Outline</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1hE0yzZbVsytClb4p4FYtYhw7XxitEwzq</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13428,6 +13571,11 @@
           <t>Airline_Cabin_Crew_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1Dej0N-EaQwqAg7RR9djUmWkjv_M4pWrj</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -13440,6 +13588,11 @@
           <t>Gerontology_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1QU31b9cR4Lg1Frz7FFMR9WoSR0DAOHkF</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -13452,6 +13605,11 @@
           <t>Flight_Instructor_Rating_Program_Outline</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1zxcdJGmKHv2OxjeNprWJKPsw5NDKqMPv</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -13464,6 +13622,11 @@
           <t>Pharmacy_Assistant_Program_Outline</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1cyk7OaYxd8oMGb_-NDWn5sbohhTSOVKC</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -13476,6 +13639,11 @@
           <t>Computer_Science_Fundamentals_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1rAqJ2Eq00ttfJFZFPiKocbPuHfY1lp0O</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -13488,6 +13656,11 @@
           <t>Network_Support_Technician_Program_Outline</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1EM1OpISsUNTbBN9pFlgAOepTwr0nVTL3</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -13500,6 +13673,11 @@
           <t>HCA_Access_Program_Outline</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1b6IVqk3CYXYxkjCsh6s49iVYTWdK6yMN</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13512,6 +13690,11 @@
           <t>Medical_Office_Assistant_Program_Outline</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10kVVqCfD4ckkIQkIWVVbMBmbuVNL7zB1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13524,6 +13707,11 @@
           <t>DBM_Coop_Program_Outline</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1UZvU1ZuSF87nZXxtOH0yHvUkcmpXmtTF</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13536,6 +13724,11 @@
           <t>Dental_Receptionist_Program_Outline</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16_YOcla93BSgR5nAlqKJa8MOFf9t_Zda</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13548,6 +13741,11 @@
           <t>Education_Assistant_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1M5zrQ5nVaO9si-P5eSfmSO7MqGWWArs3</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13560,6 +13758,11 @@
           <t>Office_Assistant_Certificate_Program_Outline</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10hXJLJNK2FlnrLSZm0TFErOfpuGuL5b6</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -13572,6 +13775,11 @@
           <t>Certificate_in_International_Trade_Program_Outline</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1puDC4sGjtSX9oLwaRUEnhLMqDkqQK-3m</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -13584,6 +13792,11 @@
           <t>Hospitality_Management_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1v1Tb2Ftx6zmyvBW6JL7TD_7LtD9-Ztx9</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -13596,6 +13809,11 @@
           <t>Accounting_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1FFWkwxutjHTGam_P5DWVTAmMqFCyB6yQ</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -13608,6 +13826,11 @@
           <t>Intl_Business_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1sZsObRNvWiXT3TbmPHPqk71OcjiYZbfc</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13620,6 +13843,11 @@
           <t>ECE_Assistant_Program_Outline</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1Cp6WRfYKbyqA3ioTN2WwAD32igmo0SGn</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -13632,6 +13860,11 @@
           <t>ESL_Program_Outline</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>16W6h6i_GQ8x09oesoBVL67bhjIEWUDfD</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -13644,6 +13877,11 @@
           <t>Medical_Device_Reprocessing_Technician_Program_Outline</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1zXVC2MbFPqIyP_BkBlQEBc_JqXfgZ8K_</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13656,6 +13894,11 @@
           <t>Medical_Lab_Assistant_Program_Outline</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>12VkMGOLNsD27LAOws72ol73nbE3GIuL5</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -13668,6 +13911,11 @@
           <t>Night_Rating_Program_Outline</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1qvMWQlFcugUtVaTNHzwOMD4PASrNIiMW</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -13680,6 +13928,11 @@
           <t>LICG_Program_Outline</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1G9kuhzeaYMShmA8k6_wyYwesCv7Nur49</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -13692,6 +13945,11 @@
           <t>Paralegal_Studies_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1esok0CQexQGJDjtIymUvFL21AY5QWScU</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -13704,6 +13962,11 @@
           <t>Dental_Assistant_Program_Outline</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>163dmrwYuBeOL8OaDsCPDN9pAtLhgiiru</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13716,6 +13979,11 @@
           <t>Hospitality_Management_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1v1Tb2Ftx6zmyvBW6JL7TD_7LtD9-Ztx9</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -13728,6 +13996,11 @@
           <t>Business_Management_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1gOiZAptf6pKmOv7M6uiU-VUG3XrTn2Dt</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -13740,6 +14013,11 @@
           <t>Accounting_PCP_Certificate_Program_Outline</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1twceBoVmmFNQuhyVNMdjamqBgAxgtpAa</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13752,6 +14030,11 @@
           <t>Bookkeeping_Accounting_Certificate_Program_Outline</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1MNa4PkcCg1lpUAlLXqQCb1WyQ36If1HH</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -13764,6 +14047,11 @@
           <t>Health_Care_Assistant_Program_Outline</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1MeL81zft6fXVsiE2pYg1gytKRoAthOhX</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -13776,6 +14064,11 @@
           <t>HCA_ESL_Program_Outline</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1IFkd9g4dt430miSNUC98AdlLM6_LDqiJ</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -13788,6 +14081,11 @@
           <t>Pharmacy_Technician_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1CLp5FMrygWOCe5tNn5vPMRXELH3wEZlw</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -13800,6 +14098,11 @@
           <t>Registered_Massage_Therapy_Program_Outline</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1_Xe6s2yu5hsIEVg0exZLR4UbsUbti2-3</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -13812,6 +14115,11 @@
           <t>Community_Support_Worker_Program_Outline</t>
         </is>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1YMlFZpSMaNMHbmlcccCofufknok0dUhM</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -13824,9 +14132,14 @@
           <t>ECE_Diploma_Program_Outline</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1LgxY5-otD3pyxN-gHn9999Q6h4N63wWD</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B64"/>
+  <autoFilter ref="A1:C64"/>
   <conditionalFormatting sqref="A2:A200">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISBLANK(A2)</formula>
